--- a/docs/sales-enablement/opros-konkurentov-cheklist.xlsx
+++ b/docs/sales-enablement/opros-konkurentov-cheklist.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Чек-лист интервью" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сравнение" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица покрытия" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,8 +81,20 @@
       <color rgb="00C97A1A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E7B4D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C97A1A"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +109,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001A2733"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +177,15 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1736,4 +1763,532 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="4.5" customWidth="1" min="2" max="2"/>
+    <col width="4.5" customWidth="1" min="3" max="3"/>
+    <col width="4.5" customWidth="1" min="4" max="4"/>
+    <col width="4.5" customWidth="1" min="5" max="5"/>
+    <col width="4.5" customWidth="1" min="6" max="6"/>
+    <col width="4.5" customWidth="1" min="7" max="7"/>
+    <col width="4.5" customWidth="1" min="8" max="8"/>
+    <col width="4.5" customWidth="1" min="9" max="9"/>
+    <col width="4.5" customWidth="1" min="10" max="10"/>
+    <col width="4.5" customWidth="1" min="11" max="11"/>
+    <col width="4.5" customWidth="1" min="12" max="12"/>
+    <col width="4.5" customWidth="1" min="13" max="13"/>
+    <col width="4.5" customWidth="1" min="14" max="14"/>
+    <col width="4.5" customWidth="1" min="15" max="15"/>
+    <col width="4.5" customWidth="1" min="16" max="16"/>
+    <col width="4.5" customWidth="1" min="17" max="17"/>
+    <col width="4.5" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Какой вопрос подтверждает какую функциональность</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>X — вопрос напрямую подтверждает пункт роадмапа. ~ — подтверждает частично. Пусто — не связано.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="110" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Контроль персональных данных</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Офлайн-образы поставки</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Гейт режима поставки</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Кросс-источниковая аналитика</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Наполнение каталога из глоссария</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Показатель как объект каталога</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Ответ из каталога</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Экспорт аудита в SIEM</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Контур подтверждения действий</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Реестр доступов агентов</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Политики на почтовые источники</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Единая оркестрация расчётов</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>Конструктор витрин</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>Внешний шлюз к моделям</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>Совместимость с /v1/responses</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>Секреты и контрольные суммы</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>Провенанс «создано моделью»</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Маскирование персональных данных в ответах?</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="16" t="n"/>
+      <c r="Q5" s="16" t="n"/>
+      <c r="R5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Развёртывание в закрытом контуре без интернета?</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Ответ сразу из нескольких систем?</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="n"/>
+      <c r="Q7" s="16" t="n"/>
+      <c r="R7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Единый справочник бизнес-показателей?</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="16" t="n"/>
+      <c r="Q8" s="16" t="n"/>
+      <c r="R8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Выгрузка логов в системы безопасности?</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="n"/>
+      <c r="Q9" s="16" t="n"/>
+      <c r="R9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Подтверждение человеком действий агента?</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="16" t="n"/>
+      <c r="O10" s="16" t="n"/>
+      <c r="P10" s="16" t="n"/>
+      <c r="Q10" s="16" t="n"/>
+      <c r="R10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Гибкая настройка доступа по папкам?</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="16" t="n"/>
+      <c r="Q11" s="16" t="n"/>
+      <c r="R11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Автоматический расчёт по данным из разных систем?</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="16" t="n"/>
+      <c r="R12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Настройка выборок данных без программиста?</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="16" t="n"/>
+      <c r="N13" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="16" t="n"/>
+      <c r="Q13" s="16" t="n"/>
+      <c r="R13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Подключение к нашим моделям / ИИ-провайдеру?</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="n"/>
+      <c r="O14" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" s="17" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="Q14" s="16" t="n"/>
+      <c r="R14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Отдельная защита паролей и ключей доступа?</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="n"/>
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="16" t="n"/>
+      <c r="N15" s="16" t="n"/>
+      <c r="O15" s="16" t="n"/>
+      <c r="P15" s="16" t="n"/>
+      <c r="Q15" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Видимость доступов агентов к системам?</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
+      <c r="R16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Отличить текст ИИ от текста человека?</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
+      <c r="R17" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/sales-enablement/opros-konkurentov-cheklist.xlsx
+++ b/docs/sales-enablement/opros-konkurentov-cheklist.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Чек-лист интервью" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сравнение" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица покрытия" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,20 +80,8 @@
       <color rgb="00C97A1A"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E7B4D"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C97A1A"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -109,11 +96,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001A2733"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -177,15 +159,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1763,532 +1736,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="4.5" customWidth="1" min="2" max="2"/>
-    <col width="4.5" customWidth="1" min="3" max="3"/>
-    <col width="4.5" customWidth="1" min="4" max="4"/>
-    <col width="4.5" customWidth="1" min="5" max="5"/>
-    <col width="4.5" customWidth="1" min="6" max="6"/>
-    <col width="4.5" customWidth="1" min="7" max="7"/>
-    <col width="4.5" customWidth="1" min="8" max="8"/>
-    <col width="4.5" customWidth="1" min="9" max="9"/>
-    <col width="4.5" customWidth="1" min="10" max="10"/>
-    <col width="4.5" customWidth="1" min="11" max="11"/>
-    <col width="4.5" customWidth="1" min="12" max="12"/>
-    <col width="4.5" customWidth="1" min="13" max="13"/>
-    <col width="4.5" customWidth="1" min="14" max="14"/>
-    <col width="4.5" customWidth="1" min="15" max="15"/>
-    <col width="4.5" customWidth="1" min="16" max="16"/>
-    <col width="4.5" customWidth="1" min="17" max="17"/>
-    <col width="4.5" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Какой вопрос подтверждает какую функциональность</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>X — вопрос напрямую подтверждает пункт роадмапа. ~ — подтверждает частично. Пусто — не связано.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="110" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Вопрос</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Контроль персональных данных</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Офлайн-образы поставки</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Гейт режима поставки</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Кросс-источниковая аналитика</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Наполнение каталога из глоссария</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Показатель как объект каталога</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Ответ из каталога</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Экспорт аудита в SIEM</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Контур подтверждения действий</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Реестр доступов агентов</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Политики на почтовые источники</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Единая оркестрация расчётов</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>Конструктор витрин</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>Внешний шлюз к моделям</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>Совместимость с /v1/responses</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Секреты и контрольные суммы</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>Провенанс «создано моделью»</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Маскирование персональных данных в ответах?</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="16" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="16" t="n"/>
-      <c r="M5" s="16" t="n"/>
-      <c r="N5" s="16" t="n"/>
-      <c r="O5" s="16" t="n"/>
-      <c r="P5" s="16" t="n"/>
-      <c r="Q5" s="16" t="n"/>
-      <c r="R5" s="16" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Развёртывание в закрытом контуре без интернета?</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="16" t="n"/>
-      <c r="M6" s="16" t="n"/>
-      <c r="N6" s="16" t="n"/>
-      <c r="O6" s="16" t="n"/>
-      <c r="P6" s="16" t="n"/>
-      <c r="Q6" s="16" t="n"/>
-      <c r="R6" s="16" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Ответ сразу из нескольких систем?</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="16" t="n"/>
-      <c r="M7" s="16" t="n"/>
-      <c r="N7" s="16" t="n"/>
-      <c r="O7" s="16" t="n"/>
-      <c r="P7" s="16" t="n"/>
-      <c r="Q7" s="16" t="n"/>
-      <c r="R7" s="16" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Единый справочник бизнес-показателей?</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="16" t="n"/>
-      <c r="N8" s="16" t="n"/>
-      <c r="O8" s="16" t="n"/>
-      <c r="P8" s="16" t="n"/>
-      <c r="Q8" s="16" t="n"/>
-      <c r="R8" s="16" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Выгрузка логов в системы безопасности?</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="16" t="n"/>
-      <c r="N9" s="16" t="n"/>
-      <c r="O9" s="16" t="n"/>
-      <c r="P9" s="16" t="n"/>
-      <c r="Q9" s="16" t="n"/>
-      <c r="R9" s="16" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Подтверждение человеком действий агента?</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="16" t="n"/>
-      <c r="M10" s="16" t="n"/>
-      <c r="N10" s="16" t="n"/>
-      <c r="O10" s="16" t="n"/>
-      <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="16" t="n"/>
-      <c r="R10" s="16" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Гибкая настройка доступа по папкам?</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="17" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="n"/>
-      <c r="N11" s="16" t="n"/>
-      <c r="O11" s="16" t="n"/>
-      <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="16" t="n"/>
-      <c r="R11" s="16" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Автоматический расчёт по данным из разных систем?</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="16" t="n"/>
-      <c r="M12" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N12" s="16" t="n"/>
-      <c r="O12" s="16" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
-      <c r="R12" s="16" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Настройка выборок данных без программиста?</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="16" t="n"/>
-      <c r="M13" s="16" t="n"/>
-      <c r="N13" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" s="16" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="16" t="n"/>
-      <c r="R13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Подключение к нашим моделям / ИИ-провайдеру?</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P14" s="17" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="Q14" s="16" t="n"/>
-      <c r="R14" s="16" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Отдельная защита паролей и ключей доступа?</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="16" t="n"/>
-      <c r="M15" s="16" t="n"/>
-      <c r="N15" s="16" t="n"/>
-      <c r="O15" s="16" t="n"/>
-      <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R15" s="16" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Видимость доступов агентов к системам?</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="16" t="n"/>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-      <c r="R16" s="16" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Отличить текст ИИ от текста человека?</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="16" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
-      <c r="M17" s="16" t="n"/>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="16" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="16" t="n"/>
-      <c r="R17" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>